--- a/docs/alliance-import-templates/03-合作成果导入模板-mock数据.xlsx
+++ b/docs/alliance-import-templates/03-合作成果导入模板-mock数据.xlsx
@@ -24,7 +24,9 @@
 成果类型：岗位成果 / 场景成果 / 课程成果 / 自定义成果（或 job / scene / course / custom），默认为 自定义成果
 描述：文本，选填
 成果日期：格式 YYYY-MM-DD，选填
-【关联参考列】（青蓝色表头，导入时忽略）：关联企业 / 关联项目 / 牵头人 为跨表单 mock 数据关联，多值用中文分号「；」分隔，需与对应导入模板中的名称保持一致</t>
+关联归属项目：项目名称，选填，多值用中文分号「；」分隔，按名称匹配导入
+关联合作企业：企业名称，选填，多值用中文分号「；」分隔，按名称匹配导入
+【关联参考列】（深蓝色表头）：牵头人 为跨表单 mock 数据关联</t>
   </si>
   <si>
     <t>成果名称 *</t>
@@ -39,10 +41,10 @@
     <t>成果日期</t>
   </si>
   <si>
-    <t>关联企业名称</t>
-  </si>
-  <si>
-    <t>关联项目名称</t>
+    <t>关联归属项目</t>
+  </si>
+  <si>
+    <t>关联合作企业</t>
   </si>
   <si>
     <t>牵头人</t>
@@ -60,12 +62,12 @@
     <t>2026-05-20</t>
   </si>
   <si>
+    <t>工业机器人视觉质检系统研发</t>
+  </si>
+  <si>
     <t>苏州华芯智能制造有限公司</t>
   </si>
   <si>
-    <t>工业机器人视觉质检系统研发</t>
-  </si>
-  <si>
     <t>王建军</t>
   </si>
   <si>
@@ -81,12 +83,12 @@
     <t>2026-03-10</t>
   </si>
   <si>
+    <t>新能源汽车电控系统实训基地建设</t>
+  </si>
+  <si>
     <t>南京云驰新能源科技有限公司</t>
   </si>
   <si>
-    <t>新能源汽车电控系统实训基地建设</t>
-  </si>
-  <si>
     <t>李敏</t>
   </si>
   <si>
@@ -102,12 +104,12 @@
     <t>2026-06-01</t>
   </si>
   <si>
+    <t>智能装备制造专业群人才共育</t>
+  </si>
+  <si>
     <t>苏州华芯智能制造有限公司；无锡智联教育装备有限公司</t>
   </si>
   <si>
-    <t>智能装备制造专业群人才共育</t>
-  </si>
-  <si>
     <t>生物医药校企协同育人调研报告</t>
   </si>
   <si>
@@ -117,10 +119,10 @@
     <t>2025-12-15</t>
   </si>
   <si>
+    <t>生物医药现代学徒制试点</t>
+  </si>
+  <si>
     <t>常州康健生物医药有限公司</t>
-  </si>
-  <si>
-    <t>生物医药现代学徒制试点</t>
   </si>
   <si>
     <t>周晓芳</t>
@@ -130,7 +132,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -147,13 +149,8 @@
       <color rgb="FF595959"/>
       <sz val="10"/>
     </font>
-    <font>
-      <family val="2"/>
-      <color rgb="FF2E74B5"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -163,6 +160,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E74B5"/>
       </patternFill>
     </fill>
     <fill>
@@ -188,10 +190,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -468,21 +470,21 @@
     <col customWidth="true" max="2" min="2" width="22"/>
     <col customWidth="true" max="3" min="3" width="52"/>
     <col customWidth="true" max="4" min="4" width="16"/>
-    <col customWidth="true" max="5" min="5" width="32"/>
-    <col customWidth="true" max="6" min="6" width="36"/>
+    <col customWidth="true" max="5" min="5" width="36"/>
+    <col customWidth="true" max="6" min="6" width="40"/>
     <col customWidth="true" max="7" min="7" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="135" customHeight="true">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="150" customHeight="true">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" ht="26" customHeight="true">
       <c r="A2" s="1" t="s">
@@ -497,13 +499,13 @@
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -520,13 +522,13 @@
       <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -543,13 +545,13 @@
       <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -566,13 +568,13 @@
       <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -589,13 +591,13 @@
       <c r="D6" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" t="s">
         <v>33</v>
       </c>
     </row>
